--- a/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
+++ b/DJF/FTs/UAH_ASW SVT_TestProcedures.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sergio\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sergio\Documents\GitHub\obdh_proy_26_Sergio_Alcocer\DJF\FTs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1FD2EC-D203-4ED7-A28B-CF31FBBCCD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3956A3B2-A1B6-4918-8A99-F9A12A05295C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Front Cover" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="133">
   <si>
     <t>Doc. No.:</t>
   </si>
@@ -332,9 +332,6 @@
   </si>
   <si>
     <t>FT_UAH_ASW_SERV_19-0110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T0 + </t>
   </si>
   <si>
     <t>STEP2</t>
@@ -442,6 +439,18 @@
   </si>
   <si>
     <t>Device Off</t>
+  </si>
+  <si>
+    <t>T0 + 3</t>
+  </si>
+  <si>
+    <t>T0 + 9</t>
+  </si>
+  <si>
+    <t>T0 + 30</t>
+  </si>
+  <si>
+    <t>T0 + 40</t>
   </si>
 </sst>
 </file>
@@ -1126,22 +1135,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1209,12 +1202,6 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1239,26 +1226,11 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1269,9 +1241,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1280,9 +1249,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1299,6 +1265,49 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3788,7 +3797,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="132" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -3799,7 +3808,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="B11" s="86"/>
+      <c r="B11" s="133"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
       </c>
@@ -3808,7 +3817,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B12" s="86"/>
+      <c r="B12" s="133"/>
       <c r="D12" s="33" t="s">
         <v>44</v>
       </c>
@@ -3817,7 +3826,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="87"/>
+      <c r="B13" s="134"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39" t="s">
         <v>45</v>
@@ -4906,7 +4915,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="132" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -4917,7 +4926,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="B11" s="86"/>
+      <c r="B11" s="133"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
       </c>
@@ -4926,7 +4935,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B12" s="86"/>
+      <c r="B12" s="133"/>
       <c r="D12" s="33" t="s">
         <v>44</v>
       </c>
@@ -4935,7 +4944,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="87"/>
+      <c r="B13" s="134"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="40"/>
@@ -6020,7 +6029,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="135" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -6031,7 +6040,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B11" s="87"/>
+      <c r="B11" s="134"/>
       <c r="C11" s="54"/>
       <c r="D11" s="54"/>
       <c r="E11" s="55"/>
@@ -8422,7 +8431,7 @@
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
       <c r="A10" s="72"/>
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="136" t="s">
         <v>81</v>
       </c>
       <c r="D10" s="69" t="s">
@@ -8434,7 +8443,7 @@
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1">
       <c r="A11" s="72"/>
-      <c r="B11" s="86"/>
+      <c r="B11" s="133"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
       </c>
@@ -8444,7 +8453,7 @@
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
       <c r="A12" s="72"/>
-      <c r="B12" s="86"/>
+      <c r="B12" s="133"/>
       <c r="D12" s="25" t="s">
         <v>45</v>
       </c>
@@ -8454,7 +8463,7 @@
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
       <c r="A13" s="72"/>
-      <c r="B13" s="87"/>
+      <c r="B13" s="134"/>
       <c r="E13" s="75"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
@@ -8507,7 +8516,7 @@
     </row>
     <row r="18" spans="1:5" ht="16.5" customHeight="1">
       <c r="A18" s="72"/>
-      <c r="B18" s="90" t="s">
+      <c r="B18" s="137" t="s">
         <v>87</v>
       </c>
       <c r="C18" s="77"/>
@@ -8520,7 +8529,7 @@
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="A19" s="72"/>
-      <c r="B19" s="91"/>
+      <c r="B19" s="138"/>
       <c r="C19" s="72"/>
       <c r="D19" s="25" t="s">
         <v>43</v>
@@ -8531,7 +8540,7 @@
     </row>
     <row r="20" spans="1:5" ht="33.75" customHeight="1">
       <c r="A20" s="72"/>
-      <c r="B20" s="91"/>
+      <c r="B20" s="138"/>
       <c r="C20" s="72"/>
       <c r="D20" s="54" t="s">
         <v>88</v>
@@ -8542,7 +8551,7 @@
     </row>
     <row r="21" spans="1:5" ht="56.25" customHeight="1">
       <c r="A21" s="44"/>
-      <c r="B21" s="92"/>
+      <c r="B21" s="139"/>
       <c r="C21" s="78"/>
       <c r="D21" s="25" t="s">
         <v>45</v>
@@ -9567,7 +9576,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="12.75" customHeight="1">
@@ -9577,632 +9586,632 @@
     </row>
     <row r="5" spans="1:5" ht="12.75" customHeight="1">
       <c r="A5" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="94"/>
     </row>
     <row r="6" spans="1:5" ht="12.75" customHeight="1">
       <c r="A6" s="44"/>
-      <c r="B6" s="105"/>
-      <c r="C6" s="111" t="s">
+      <c r="B6" s="97"/>
+      <c r="C6" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="104" t="s">
+      <c r="D6" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="96" t="s">
+      <c r="E6" s="88" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.5" customHeight="1">
       <c r="A7" s="72"/>
-      <c r="B7" s="112" t="s">
+      <c r="B7" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="85"/>
+      <c r="D7" s="105" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="87" t="s">
         <v>104</v>
-      </c>
-      <c r="C7" s="93"/>
-      <c r="D7" s="113" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="95" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="12.75" customHeight="1">
       <c r="A8" s="72"/>
-      <c r="B8" s="114"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="97"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="89"/>
     </row>
     <row r="9" spans="1:5" ht="12.75" customHeight="1">
       <c r="A9" s="44"/>
-      <c r="B9" s="105"/>
-      <c r="C9" s="115" t="s">
+      <c r="B9" s="97"/>
+      <c r="C9" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="98" t="s">
+      <c r="E9" s="90" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
       <c r="A10" s="72"/>
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="93"/>
-      <c r="D10" s="110" t="s">
+      <c r="C10" s="85"/>
+      <c r="D10" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="99" t="s">
+      <c r="E10" s="91" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1">
       <c r="A11" s="72"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="113" t="s">
+      <c r="B11" s="147"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="97" t="s">
+      <c r="E11" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1">
       <c r="A12" s="72"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="113" t="s">
+      <c r="B12" s="147"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="97" t="s">
+      <c r="E12" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
       <c r="A13" s="72"/>
-      <c r="B13" s="117"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="100"/>
+      <c r="B13" s="148"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="92"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
       <c r="A14" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" s="118" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="108" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="107" t="s">
+      <c r="C14" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="107" t="s">
+      <c r="D14" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="101" t="s">
+      <c r="E14" s="93" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="12.75" customHeight="1">
       <c r="A15" s="72"/>
-      <c r="B15" s="112"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="99"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="91"/>
     </row>
     <row r="16" spans="1:5" ht="66" customHeight="1">
       <c r="A16" s="72"/>
-      <c r="B16" s="114" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="93"/>
-      <c r="D16" s="119" t="s">
+      <c r="B16" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="95" t="s">
-        <v>109</v>
+      <c r="C16" s="85"/>
+      <c r="D16" s="109" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="87" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="33.75" customHeight="1">
       <c r="A17" s="44"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="106" t="s">
+      <c r="B17" s="85"/>
+      <c r="C17" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="106" t="s">
+      <c r="D17" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="98" t="s">
+      <c r="E17" s="90" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="12.75" customHeight="1">
       <c r="A18" s="72"/>
-      <c r="B18" s="89" t="s">
+      <c r="B18" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="93"/>
-      <c r="D18" s="110" t="s">
+      <c r="C18" s="85"/>
+      <c r="D18" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="99" t="s">
+      <c r="E18" s="91" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="12.75" customHeight="1">
       <c r="A19" s="72"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="113" t="s">
+      <c r="B19" s="147"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="97" t="s">
+      <c r="E19" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="12.75" customHeight="1">
       <c r="A20" s="72"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="113" t="s">
+      <c r="B20" s="147"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="97" t="s">
+      <c r="E20" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="12.75" customHeight="1">
       <c r="A21" s="72"/>
-      <c r="B21" s="117"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="100"/>
+      <c r="B21" s="148"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="92"/>
     </row>
     <row r="22" spans="1:5" ht="12.75" customHeight="1">
       <c r="A22" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="108" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="118" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="107" t="s">
+      <c r="C22" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="107" t="s">
+      <c r="D22" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="101" t="s">
+      <c r="E22" s="93" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="12.75" customHeight="1">
       <c r="A23" s="72"/>
-      <c r="B23" s="120" t="s">
+      <c r="B23" s="110" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="102"/>
+      <c r="D23" s="111" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="100" t="s">
         <v>110</v>
-      </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="121" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="108" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="12.75" customHeight="1">
       <c r="A24" s="72"/>
-      <c r="B24" s="114"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="113"/>
-      <c r="E24" s="103"/>
+      <c r="B24" s="106"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5" ht="12.75" customHeight="1">
       <c r="A25" s="44"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="106" t="s">
+      <c r="B25" s="85"/>
+      <c r="C25" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="106" t="s">
+      <c r="D25" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="98" t="s">
+      <c r="E25" s="90" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="12.75" customHeight="1">
       <c r="A26" s="72"/>
-      <c r="B26" s="89" t="s">
+      <c r="B26" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="93"/>
-      <c r="D26" s="110" t="s">
+      <c r="C26" s="85"/>
+      <c r="D26" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="99" t="s">
+      <c r="E26" s="91" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="12.75" customHeight="1">
       <c r="A27" s="72"/>
-      <c r="B27" s="116"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="113" t="s">
+      <c r="B27" s="147"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="97" t="s">
+      <c r="E27" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="12.75" customHeight="1">
       <c r="A28" s="72"/>
-      <c r="B28" s="116"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="113" t="s">
+      <c r="B28" s="147"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="97" t="s">
+      <c r="E28" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="12.75" customHeight="1">
       <c r="A29" s="72"/>
-      <c r="B29" s="117"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="100"/>
+      <c r="B29" s="148"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="92"/>
     </row>
     <row r="30" spans="1:5" ht="12.75" customHeight="1">
       <c r="A30" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" s="118" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="107" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="108" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="107" t="s">
+      <c r="D30" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="101" t="s">
+      <c r="E30" s="93" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
       <c r="A31" s="72"/>
-      <c r="B31" s="122" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="110"/>
-      <c r="D31" s="123" t="s">
+      <c r="B31" s="112" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="102"/>
+      <c r="D31" s="113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="100" t="s">
         <v>114</v>
-      </c>
-      <c r="E31" s="108" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="12.75" customHeight="1">
       <c r="A32" s="72"/>
-      <c r="B32" s="124" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" s="93"/>
-      <c r="D32" s="113"/>
-      <c r="E32" s="103"/>
+      <c r="B32" s="114" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="85"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="95"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1">
       <c r="A33" s="44"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="106" t="s">
+      <c r="B33" s="85"/>
+      <c r="C33" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="106" t="s">
+      <c r="D33" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="98" t="s">
+      <c r="E33" s="90" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1">
       <c r="A34" s="72"/>
-      <c r="B34" s="89" t="s">
+      <c r="B34" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="93"/>
-      <c r="D34" s="110" t="s">
+      <c r="C34" s="85"/>
+      <c r="D34" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="99" t="s">
+      <c r="E34" s="91" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1">
       <c r="A35" s="72"/>
-      <c r="B35" s="116"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="113" t="s">
+      <c r="B35" s="147"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="97" t="s">
+      <c r="E35" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1">
       <c r="A36" s="72"/>
-      <c r="B36" s="116"/>
-      <c r="C36" s="93"/>
-      <c r="D36" s="113" t="s">
+      <c r="B36" s="147"/>
+      <c r="C36" s="85"/>
+      <c r="D36" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="97" t="s">
+      <c r="E36" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1">
       <c r="A37" s="72"/>
-      <c r="B37" s="117"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="100"/>
+      <c r="B37" s="148"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="92"/>
     </row>
     <row r="38" spans="1:5" ht="12.75" customHeight="1">
       <c r="A38" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="118" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" s="107" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="108" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="107" t="s">
+      <c r="D38" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="E38" s="101" t="s">
+      <c r="E38" s="93" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="12.75" customHeight="1">
       <c r="A39" s="72"/>
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="86" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="102"/>
+      <c r="D39" s="86" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="115" t="s">
         <v>116</v>
-      </c>
-      <c r="C39" s="110"/>
-      <c r="D39" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39" s="125" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.75" customHeight="1">
       <c r="A40" s="72"/>
-      <c r="B40" s="114"/>
-      <c r="C40" s="93"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="103"/>
+      <c r="B40" s="106"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="41" spans="1:5" ht="12.75" customHeight="1">
       <c r="A41" s="44"/>
-      <c r="B41" s="93"/>
-      <c r="C41" s="106" t="s">
+      <c r="B41" s="85"/>
+      <c r="C41" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="106" t="s">
+      <c r="D41" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="98" t="s">
+      <c r="E41" s="90" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="12.75" customHeight="1">
       <c r="A42" s="72"/>
-      <c r="B42" s="89" t="s">
+      <c r="B42" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="93"/>
-      <c r="D42" s="110" t="s">
+      <c r="C42" s="85"/>
+      <c r="D42" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="E42" s="99" t="s">
+      <c r="E42" s="91" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="12.75" customHeight="1">
       <c r="A43" s="72"/>
-      <c r="B43" s="116"/>
-      <c r="C43" s="93"/>
-      <c r="D43" s="113" t="s">
+      <c r="B43" s="147"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="97" t="s">
+      <c r="E43" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="12.75" customHeight="1">
       <c r="A44" s="72"/>
-      <c r="B44" s="116"/>
-      <c r="C44" s="93"/>
-      <c r="D44" s="113" t="s">
+      <c r="B44" s="147"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="97" t="s">
+      <c r="E44" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="12.75" customHeight="1">
       <c r="A45" s="72"/>
-      <c r="B45" s="117"/>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="100"/>
+      <c r="B45" s="148"/>
+      <c r="C45" s="85"/>
+      <c r="D45" s="85"/>
+      <c r="E45" s="92"/>
     </row>
     <row r="46" spans="1:5" ht="12.75" customHeight="1">
       <c r="A46" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="B46" s="118" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="107" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="108" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D46" s="107" t="s">
+      <c r="D46" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="E46" s="101" t="s">
+      <c r="E46" s="93" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="12.75" customHeight="1">
       <c r="A47" s="72"/>
-      <c r="B47" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="C47" s="110"/>
-      <c r="D47" s="94" t="s">
+      <c r="B47" s="86" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="102"/>
+      <c r="D47" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="E47" s="125" t="s">
-        <v>119</v>
+      <c r="E47" s="115" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="12.75" customHeight="1">
       <c r="A48" s="72"/>
-      <c r="B48" s="114"/>
-      <c r="C48" s="93"/>
-      <c r="D48" s="113"/>
-      <c r="E48" s="103"/>
+      <c r="B48" s="106"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="95"/>
     </row>
     <row r="49" spans="1:5" ht="12.75" customHeight="1">
       <c r="A49" s="44"/>
-      <c r="B49" s="93"/>
-      <c r="C49" s="130" t="s">
+      <c r="B49" s="85"/>
+      <c r="C49" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="D49" s="130" t="s">
+      <c r="D49" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="E49" s="131" t="s">
+      <c r="E49" s="117" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1">
       <c r="A50" s="72"/>
-      <c r="B50" s="132" t="s">
-        <v>121</v>
-      </c>
-      <c r="C50" s="133"/>
-      <c r="D50" s="134" t="s">
+      <c r="B50" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="118"/>
+      <c r="D50" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="135" t="s">
+      <c r="E50" s="120" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="12.75" customHeight="1">
       <c r="A51" s="72"/>
-      <c r="B51" s="136"/>
-      <c r="C51" s="137"/>
-      <c r="D51" s="138" t="s">
+      <c r="B51" s="141"/>
+      <c r="C51" s="121"/>
+      <c r="D51" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="E51" s="139" t="s">
+      <c r="E51" s="123" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="12.75" customHeight="1">
       <c r="A52" s="72"/>
-      <c r="B52" s="136"/>
-      <c r="C52" s="137"/>
-      <c r="D52" s="138" t="s">
+      <c r="B52" s="141"/>
+      <c r="C52" s="121"/>
+      <c r="D52" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="E52" s="139" t="s">
+      <c r="E52" s="123" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="12.75" customHeight="1">
       <c r="A53" s="72"/>
-      <c r="B53" s="140"/>
-      <c r="C53" s="141"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="142"/>
+      <c r="B53" s="142"/>
+      <c r="C53" s="124"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="125"/>
     </row>
     <row r="54" spans="1:5" ht="29.25" customHeight="1">
-      <c r="B54" s="128" t="s">
+      <c r="B54" s="145" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="126"/>
+      <c r="D54" s="126" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="130" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B55" s="146"/>
+      <c r="C55" s="127"/>
+      <c r="D55" s="127"/>
+      <c r="E55" s="128"/>
+    </row>
+    <row r="56" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B56" s="145" t="s">
         <v>122</v>
       </c>
-      <c r="C54" s="143"/>
-      <c r="D54" s="143" t="s">
+      <c r="C56" s="126"/>
+      <c r="D56" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="147" t="s">
+      <c r="E56" s="115" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B57" s="146"/>
+      <c r="C57" s="127"/>
+      <c r="D57" s="127"/>
+      <c r="E57" s="128"/>
+    </row>
+    <row r="58" spans="1:5" ht="12.75" customHeight="1">
+      <c r="B58" s="143" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="126"/>
+      <c r="D58" s="122" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" s="131" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B55" s="129"/>
-      <c r="C55" s="144"/>
-      <c r="D55" s="144"/>
-      <c r="E55" s="145"/>
-    </row>
-    <row r="56" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B56" s="128" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="143"/>
-      <c r="D56" s="94" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56" s="125" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B57" s="129"/>
-      <c r="C57" s="144"/>
-      <c r="D57" s="144"/>
-      <c r="E57" s="145"/>
-    </row>
-    <row r="58" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B58" s="126" t="s">
-        <v>124</v>
-      </c>
-      <c r="C58" s="143"/>
-      <c r="D58" s="138" t="s">
-        <v>43</v>
-      </c>
-      <c r="E58" s="148" t="s">
-        <v>129</v>
-      </c>
-    </row>
     <row r="59" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B59" s="127"/>
-      <c r="C59" s="146"/>
-      <c r="D59" s="138" t="s">
+      <c r="B59" s="144"/>
+      <c r="C59" s="129"/>
+      <c r="D59" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="E59" s="139" t="s">
+      <c r="E59" s="123" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B60" s="127"/>
-      <c r="C60" s="146"/>
+      <c r="B60" s="144"/>
+      <c r="C60" s="129"/>
     </row>
     <row r="61" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B61" s="127"/>
-      <c r="C61" s="144"/>
-      <c r="D61" s="144"/>
-      <c r="E61" s="145"/>
+      <c r="B61" s="144"/>
+      <c r="C61" s="127"/>
+      <c r="D61" s="127"/>
+      <c r="E61" s="128"/>
     </row>
     <row r="62" spans="1:5" ht="12.75" customHeight="1"/>
     <row r="63" spans="1:5" ht="12.75" customHeight="1"/>
@@ -11246,7 +11255,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="132" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="79"/>
@@ -11258,7 +11267,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="B11" s="86"/>
+      <c r="B11" s="133"/>
       <c r="C11" s="81"/>
       <c r="D11" s="25" t="s">
         <v>43</v>
@@ -11268,7 +11277,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.25" customHeight="1">
-      <c r="B12" s="87"/>
+      <c r="B12" s="134"/>
       <c r="C12" s="82"/>
       <c r="D12" s="39" t="s">
         <v>45</v>
@@ -11278,7 +11287,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="132" t="s">
         <v>96</v>
       </c>
       <c r="C13" s="79"/>
@@ -11286,12 +11295,12 @@
       <c r="E13" s="83"/>
     </row>
     <row r="14" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B14" s="86"/>
+      <c r="B14" s="133"/>
       <c r="C14" s="81"/>
       <c r="E14" s="34"/>
     </row>
     <row r="15" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B15" s="87"/>
+      <c r="B15" s="134"/>
       <c r="C15" s="82"/>
       <c r="D15" s="39"/>
       <c r="E15" s="40"/>
